--- a/data/trans_dic/P34A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,65; 52,68</t>
+          <t>46,59; 52,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,12; 28,71</t>
+          <t>22,98; 28,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,42; 50,76</t>
+          <t>43,53; 50,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,58; 55,7</t>
+          <t>47,39; 55,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,14; 54,75</t>
+          <t>49,34; 54,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,38; 39,11</t>
+          <t>33,69; 39,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,03; 59,68</t>
+          <t>53,16; 59,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,17; 63,49</t>
+          <t>57,97; 63,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,97; 52,96</t>
+          <t>48,92; 53,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,05; 33,66</t>
+          <t>29,85; 33,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,83; 54,77</t>
+          <t>50,2; 54,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,55; 59,01</t>
+          <t>54,45; 59,17</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,01; 43,12</t>
+          <t>38,09; 42,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 24,95</t>
+          <t>20,9; 24,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,9; 34,17</t>
+          <t>29,77; 34,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 32,39</t>
+          <t>19,86; 32,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,86; 46,13</t>
+          <t>41,17; 46,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,07; 32,48</t>
+          <t>28,05; 32,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,78; 42,13</t>
+          <t>37,55; 42,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,61; 38,74</t>
+          <t>25,12; 38,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,11; 43,68</t>
+          <t>40,2; 43,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,92; 27,9</t>
+          <t>24,81; 27,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,29; 37,4</t>
+          <t>34,33; 37,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,33; 34,68</t>
+          <t>24,91; 35,22</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,08; 30,89</t>
+          <t>23,51; 31,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,7; 17,38</t>
+          <t>10,56; 17,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,48; 26,71</t>
+          <t>19,32; 26,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,16; 27,05</t>
+          <t>19,87; 27,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,95; 43,49</t>
+          <t>34,08; 42,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,69; 22,18</t>
+          <t>14,63; 22,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,61; 32,94</t>
+          <t>24,86; 32,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,4; 29,36</t>
+          <t>23,5; 29,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,27; 35,53</t>
+          <t>29,32; 35,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 18,28</t>
+          <t>13,5; 18,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,87; 28,62</t>
+          <t>23,22; 28,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 27,08</t>
+          <t>22,61; 27,27</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,54; 42,93</t>
+          <t>39,27; 42,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,97; 23,98</t>
+          <t>21,12; 24,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,31; 35,49</t>
+          <t>32,27; 35,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,7; 33,76</t>
+          <t>23,92; 33,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,33; 47,97</t>
+          <t>44,47; 47,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,28; 32,62</t>
+          <t>29,34; 32,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,82; 44,44</t>
+          <t>40,91; 44,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,98; 41,16</t>
+          <t>31,91; 41,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,41; 44,94</t>
+          <t>42,38; 44,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 27,79</t>
+          <t>25,73; 27,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,2; 39,48</t>
+          <t>37,2; 39,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,57; 36,92</t>
+          <t>29,45; 37,07</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>473457; 534661</t>
+          <t>472880; 536400</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>225108; 279577</t>
+          <t>223727; 277762</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>327570; 382879</t>
+          <t>328363; 381874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243316; 284892</t>
+          <t>242348; 283405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>635503; 707950</t>
+          <t>638055; 710051</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>446170; 522760</t>
+          <t>450354; 523911</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>527476; 593572</t>
+          <t>528798; 593866</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>436058; 475885</t>
+          <t>434511; 476273</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1130134; 1222320</t>
+          <t>1129073; 1227420</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>694340; 777762</t>
+          <t>689702; 784902</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>871467; 957900</t>
+          <t>878087; 958231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>687830; 744130</t>
+          <t>686643; 746146</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>634746; 719988</t>
+          <t>636031; 717090</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>411651; 489726</t>
+          <t>410198; 489969</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>620776; 709492</t>
+          <t>618059; 708822</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>428924; 740283</t>
+          <t>453954; 744729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>637248; 719453</t>
+          <t>642124; 719467</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>493384; 570929</t>
+          <t>493071; 571957</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>751145; 837587</t>
+          <t>746579; 835102</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>550071; 865965</t>
+          <t>561571; 866077</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1295256; 1410719</t>
+          <t>1298427; 1410523</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>927153; 1038157</t>
+          <t>923247; 1033916</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1393708; 1520251</t>
+          <t>1395403; 1515975</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1145335; 1567990</t>
+          <t>1126116; 1592285</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>126193; 168937</t>
+          <t>128540; 173276</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51479; 83644</t>
+          <t>50836; 82627</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106558; 146048</t>
+          <t>105643; 147545</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130142; 174601</t>
+          <t>128283; 175882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>158186; 202626</t>
+          <t>158789; 199821</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67353; 101741</t>
+          <t>67113; 101668</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>135158; 180909</t>
+          <t>136504; 177786</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>154468; 193801</t>
+          <t>155106; 194929</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>296421; 359776</t>
+          <t>296905; 359422</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125761; 171791</t>
+          <t>126848; 174284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>250615; 313715</t>
+          <t>254448; 312730</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>292354; 353549</t>
+          <t>295167; 356072</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1277681; 1387470</t>
+          <t>1269057; 1384498</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>716600; 819659</t>
+          <t>721725; 821006</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1091393; 1198720</t>
+          <t>1089899; 1200840</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>781516; 1162127</t>
+          <t>823313; 1170032</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1471330; 1592159</t>
+          <t>1475908; 1591174</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1040181; 1159173</t>
+          <t>1042616; 1154525</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1441704; 1569618</t>
+          <t>1445027; 1565189</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1165871; 1500338</t>
+          <t>1163248; 1509427</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2777688; 2943935</t>
+          <t>2775725; 2940722</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1786660; 1937543</t>
+          <t>1793730; 1944759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2570205; 2727966</t>
+          <t>2570666; 2729724</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2095982; 2616851</t>
+          <t>2087516; 2627564</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,59; 52,85</t>
+          <t>46,62; 52,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 28,53</t>
+          <t>22,99; 28,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,53; 50,62</t>
+          <t>43,63; 50,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,39; 55,41</t>
+          <t>47,97; 55,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,34; 54,91</t>
+          <t>49,54; 55,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,69; 39,19</t>
+          <t>33,85; 39,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,16; 59,71</t>
+          <t>52,99; 59,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,97; 63,54</t>
+          <t>58,08; 63,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,92; 53,18</t>
+          <t>49,01; 52,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,85; 33,97</t>
+          <t>29,78; 33,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,2; 54,79</t>
+          <t>49,87; 54,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,45; 59,17</t>
+          <t>54,82; 59,05</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,09; 42,94</t>
+          <t>38,04; 42,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 24,96</t>
+          <t>20,97; 25,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,77; 34,14</t>
+          <t>29,73; 34,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,86; 32,58</t>
+          <t>29,68; 34,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,17; 46,13</t>
+          <t>41,0; 46,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,05; 32,54</t>
+          <t>28,03; 32,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,55; 42,0</t>
+          <t>37,79; 42,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,12; 38,74</t>
+          <t>35,64; 39,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,2; 43,68</t>
+          <t>40,21; 43,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,81; 27,79</t>
+          <t>24,71; 27,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,33; 37,3</t>
+          <t>34,24; 37,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 35,22</t>
+          <t>33,09; 36,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,51; 31,69</t>
+          <t>23,08; 31,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 17,17</t>
+          <t>10,18; 17,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 26,98</t>
+          <t>19,42; 26,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,87; 27,24</t>
+          <t>20,18; 27,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,08; 42,89</t>
+          <t>34,36; 43,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,63; 22,17</t>
+          <t>14,36; 22,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,86; 32,38</t>
+          <t>24,64; 32,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,5; 29,53</t>
+          <t>24,07; 29,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,32; 35,49</t>
+          <t>29,35; 35,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 18,54</t>
+          <t>13,59; 18,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,22; 28,53</t>
+          <t>22,86; 28,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,61; 27,27</t>
+          <t>23,01; 27,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,27; 42,84</t>
+          <t>39,18; 42,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,12; 24,02</t>
+          <t>21,0; 24,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,27; 35,55</t>
+          <t>32,23; 35,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,92; 33,99</t>
+          <t>31,75; 35,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,47; 47,94</t>
+          <t>44,36; 47,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,34; 32,49</t>
+          <t>29,23; 32,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,91; 44,31</t>
+          <t>41,17; 44,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,91; 41,41</t>
+          <t>39,09; 42,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,38; 44,89</t>
+          <t>42,42; 44,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,73; 27,9</t>
+          <t>25,66; 27,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,2; 39,51</t>
+          <t>37,25; 39,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,45; 37,07</t>
+          <t>35,98; 38,17</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262206</t>
+          <t>297056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>455086</t>
+          <t>493839</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>717292</t>
+          <t>790895</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>472880; 536400</t>
+          <t>473110; 535252</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>223727; 277762</t>
+          <t>223853; 279434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>328363; 381874</t>
+          <t>329121; 382155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>242348; 283405</t>
+          <t>275608; 319875</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>638055; 710051</t>
+          <t>640641; 711258</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>450354; 523911</t>
+          <t>452419; 524013</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>528798; 593866</t>
+          <t>527084; 590628</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>434511; 476273</t>
+          <t>474250; 515894</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1129073; 1227420</t>
+          <t>1131113; 1222782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>689702; 784902</t>
+          <t>688118; 780820</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>878087; 958231</t>
+          <t>872266; 958412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>686643; 746146</t>
+          <t>762561; 821392</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>647976</t>
+          <t>707859</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>756204</t>
+          <t>815303</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1404179</t>
+          <t>1523162</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>636031; 717090</t>
+          <t>635254; 716991</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>410198; 489969</t>
+          <t>411600; 491841</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>618059; 708822</t>
+          <t>617330; 708852</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>453954; 744729</t>
+          <t>660688; 766270</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>642124; 719467</t>
+          <t>639499; 718132</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>493071; 571957</t>
+          <t>492753; 571204</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>746579; 835102</t>
+          <t>751320; 838021</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>561571; 866077</t>
+          <t>772764; 860698</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1298427; 1410523</t>
+          <t>1298559; 1409638</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>923247; 1033916</t>
+          <t>919325; 1033926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1395403; 1515975</t>
+          <t>1391805; 1517228</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1126116; 1592285</t>
+          <t>1454160; 1587229</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151195</t>
+          <t>166663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>172655</t>
+          <t>196396</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>323851</t>
+          <t>363059</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>128540; 173276</t>
+          <t>126197; 169560</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50836; 82627</t>
+          <t>48997; 82778</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105643; 147545</t>
+          <t>106215; 145295</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128283; 175882</t>
+          <t>143344; 193520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>158789; 199821</t>
+          <t>160100; 203958</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67113; 101668</t>
+          <t>65882; 101483</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>136504; 177786</t>
+          <t>135320; 178153</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>155106; 194929</t>
+          <t>176775; 219275</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>296905; 359422</t>
+          <t>297206; 357533</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126848; 174284</t>
+          <t>127682; 173501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>254448; 312730</t>
+          <t>250591; 313396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>295167; 356072</t>
+          <t>332513; 395650</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1061378</t>
+          <t>1171578</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1383945</t>
+          <t>1505538</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2445323</t>
+          <t>2677115</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1269057; 1384498</t>
+          <t>1266243; 1378935</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>721725; 821006</t>
+          <t>717709; 822073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1089899; 1200840</t>
+          <t>1088595; 1197600</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>823313; 1170032</t>
+          <t>1114665; 1238218</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1475908; 1591174</t>
+          <t>1472231; 1591192</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1042616; 1154525</t>
+          <t>1038610; 1153094</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1445027; 1565189</t>
+          <t>1454193; 1572667</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1163248; 1509427</t>
+          <t>1454104; 1562423</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2775725; 2940722</t>
+          <t>2778487; 2944256</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1793730; 1944759</t>
+          <t>1788887; 1945040</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2570666; 2729724</t>
+          <t>2574073; 2739930</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2087516; 2627564</t>
+          <t>2601492; 2759777</t>
         </is>
       </c>
     </row>
